--- a/samples/Sample_8_For_School_Management_Section_B_Class7.xlsx
+++ b/samples/Sample_8_For_School_Management_Section_B_Class7.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vikram Patel</t>
+          <t>Reyansh Kulkarni</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aadhya Rao</t>
+          <t>Meera Joshi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yash Nair</t>
+          <t>Reyansh Sharma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meera Nair</t>
+          <t>Sneha Shetty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sameer Singh</t>
+          <t>Aarav Reddy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diya Bhat</t>
+          <t>Priya Murthy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sameer Desai</t>
+          <t>Pranav Sharma</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aadhya Nair</t>
+          <t>Kritika Patel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Krishna Kulkarni</t>
+          <t>Rohan Shetty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anjali Iyer</t>
+          <t>Aadhya Prabhu</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vivaan Naik</t>
+          <t>Ishaan Nair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Swathi Naik</t>
+          <t>Kavya Pai</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vihaan Pai</t>
+          <t>Ishaan Desai</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tanya Bhat</t>
+          <t>Pooja Hegde</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nikhil Nair</t>
+          <t>Rohan Kumar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Divya Desai</t>
+          <t>Neha Shetty</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aarav Verma</t>
+          <t>Krishna Shetty</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Meera Kulkarni</t>
+          <t>Nisha Patel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vivaan Bhat</t>
+          <t>Siddharth Gowda</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kavya Sharma</t>
+          <t>Tanya Bhat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Karthik Prabhu</t>
+          <t>Sameer Kulkarni</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Priya Gowda</t>
+          <t>Neha Kumar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rahul Desai</t>
+          <t>Aditya Iyer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sara Sharma</t>
+          <t>Myra Verma</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vihaan Gowda</t>
+          <t>Rohan Hegde</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anjali Hegde</t>
+          <t>Nisha Rao</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pranav Iyer</t>
+          <t>Akash Kulkarni</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Riya Shetty</t>
+          <t>Divya Kulkarni</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sameer Joshi</t>
+          <t>Ishaan Rao</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tanya Joshi</t>
+          <t>Meera Pai</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1615,33 +1615,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
+        <v>39</v>
+      </c>
+      <c r="D2" t="n">
         <v>43</v>
       </c>
-      <c r="D2" t="n">
-        <v>38</v>
-      </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Perimeter &amp; Area</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1650,19 +1642,19 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>29</v>
+      </c>
+      <c r="C3" t="n">
         <v>31</v>
       </c>
-      <c r="C3" t="n">
-        <v>29</v>
-      </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
         <v>31</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1681,26 +1673,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
+          <t>Lines &amp; Angles</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1712,28 +1704,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Simple Equations</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1743,16 +1731,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" t="n">
         <v>19</v>
@@ -1760,7 +1748,11 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ratio &amp; Proportion</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1770,26 +1762,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" t="n">
         <v>9</v>
       </c>
-      <c r="D7" t="n">
-        <v>8</v>
-      </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Perimeter &amp; Area</t>
+          <t>Lines &amp; Angles</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1801,24 +1793,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" t="n">
         <v>42</v>
       </c>
-      <c r="D8" t="n">
-        <v>39</v>
-      </c>
       <c r="E8" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1828,16 +1824,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
         <v>31</v>
@@ -1847,7 +1843,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
+          <t>Fractions &amp; Decimals</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1862,21 +1858,25 @@
         <v>44</v>
       </c>
       <c r="C10" t="n">
+        <v>46</v>
+      </c>
+      <c r="D10" t="n">
+        <v>44</v>
+      </c>
+      <c r="E10" t="n">
         <v>43</v>
       </c>
-      <c r="D10" t="n">
-        <v>46</v>
-      </c>
-      <c r="E10" t="n">
-        <v>45</v>
-      </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Perimeter &amp; Area</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1889,13 +1889,13 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
         <v>15</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
+          <t>Fractions &amp; Decimals</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1917,26 +1917,26 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
+          <t>Fractions &amp; Decimals</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1948,26 +1948,26 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
+          <t>Simple Equations</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1979,33 +1979,29 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
         <v>31</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Simple Equations</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>On track, but should aim higher with focused practice.</t>
-        </is>
-      </c>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2014,33 +2010,29 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>22</v>
+      </c>
+      <c r="C15" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" t="n">
         <v>23</v>
       </c>
-      <c r="C15" t="n">
-        <v>18</v>
-      </c>
-      <c r="D15" t="n">
-        <v>18</v>
-      </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fractions &amp; Decimals</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
-        </is>
-      </c>
+          <t>Simple Equations</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2049,20 +2041,20 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
+        <v>18</v>
+      </c>
+      <c r="D16" t="n">
         <v>17</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>18</v>
+      </c>
+      <c r="F16" t="n">
         <v>14</v>
       </c>
-      <c r="E16" t="n">
-        <v>14</v>
-      </c>
-      <c r="F16" t="n">
-        <v>17</v>
-      </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
@@ -2073,7 +2065,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Below expectations — recommend extra classes after school.</t>
+          <t>Struggling with fundamentals, needs remedial sessions.</t>
         </is>
       </c>
     </row>
@@ -2084,13 +2076,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>9</v>
@@ -2115,19 +2107,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C18" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -2145,25 +2137,21 @@
         <v>33</v>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -2173,16 +2161,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D20" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E20" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F20" t="n">
         <v>46</v>
@@ -2203,21 +2191,25 @@
         <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" t="n">
         <v>14</v>
       </c>
-      <c r="E21" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" t="n">
-        <v>19</v>
-      </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ratio &amp; Proportion</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -2227,29 +2219,33 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C22" t="n">
+        <v>35</v>
+      </c>
+      <c r="D22" t="n">
+        <v>35</v>
+      </c>
+      <c r="E22" t="n">
         <v>41</v>
       </c>
-      <c r="D22" t="n">
-        <v>42</v>
-      </c>
-      <c r="E22" t="n">
-        <v>39</v>
-      </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Perimeter &amp; Area</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Strong performer, small gains possible with more practice.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2258,28 +2254,24 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>24</v>
+      </c>
+      <c r="C23" t="n">
         <v>28</v>
       </c>
-      <c r="C23" t="n">
-        <v>31</v>
-      </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Fractions &amp; Decimals</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -2289,26 +2281,26 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>28</v>
+      </c>
+      <c r="C24" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>26</v>
+      </c>
+      <c r="E24" t="n">
+        <v>26</v>
+      </c>
+      <c r="F24" t="n">
         <v>29</v>
       </c>
-      <c r="C24" t="n">
-        <v>32</v>
-      </c>
-      <c r="D24" t="n">
-        <v>30</v>
-      </c>
-      <c r="E24" t="n">
-        <v>29</v>
-      </c>
-      <c r="F24" t="n">
-        <v>31</v>
-      </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
+          <t>Fractions &amp; Decimals</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2320,26 +2312,26 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C25" t="n">
+        <v>18</v>
+      </c>
+      <c r="D25" t="n">
         <v>21</v>
       </c>
-      <c r="D25" t="n">
-        <v>17</v>
-      </c>
       <c r="E25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
+          <t>Perimeter &amp; Area</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2351,28 +2343,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2382,31 +2370,27 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Very low scores across the board, please involve parents.</t>
+          <t>Serious concern — immediate intervention needed.</t>
         </is>
       </c>
     </row>
@@ -2417,28 +2401,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" t="n">
         <v>43</v>
       </c>
       <c r="D28" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Perimeter &amp; Area</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2448,26 +2428,26 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C29" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D29" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F29" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Perimeter &amp; Area</t>
+          <t>Fractions &amp; Decimals</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -2479,28 +2459,24 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D30" t="n">
+        <v>43</v>
+      </c>
+      <c r="E30" t="n">
+        <v>43</v>
+      </c>
+      <c r="F30" t="n">
         <v>46</v>
       </c>
-      <c r="E30" t="n">
-        <v>50</v>
-      </c>
-      <c r="F30" t="n">
-        <v>47</v>
-      </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2510,28 +2486,24 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Perimeter &amp; Area</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
@@ -2616,21 +2588,25 @@
         <v>82</v>
       </c>
       <c r="C2" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Heat</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -2644,19 +2620,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C3" t="n">
         <v>67</v>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2666,7 +2642,11 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Average performance — revision of basics recommended.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2678,25 +2658,21 @@
         <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Acids Bases &amp; Salts</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -2706,33 +2682,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E5" t="n">
         <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Below expectations — recommend extra classes after school.</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2741,25 +2709,33 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E6" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
         <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Weather &amp; Climate</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Struggling with fundamentals, needs remedial sessions.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2768,26 +2744,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2799,29 +2775,29 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D8" t="n">
+        <v>62</v>
+      </c>
+      <c r="E8" t="n">
         <v>61</v>
       </c>
-      <c r="E8" t="n">
-        <v>65</v>
-      </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Was doing well earlier, something seems to be affecting focus now.</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Weather &amp; Climate</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2830,25 +2806,29 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2857,25 +2837,33 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C10" t="n">
+        <v>98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>92</v>
+      </c>
+      <c r="E10" t="n">
+        <v>92</v>
+      </c>
+      <c r="F10" t="n">
         <v>94</v>
       </c>
-      <c r="D10" t="n">
-        <v>88</v>
-      </c>
-      <c r="E10" t="n">
-        <v>89</v>
-      </c>
-      <c r="F10" t="n">
-        <v>87</v>
-      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Nutrition in Plants</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2887,23 +2875,23 @@
         <v>41</v>
       </c>
       <c r="C11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D11" t="n">
+        <v>43</v>
+      </c>
+      <c r="E11" t="n">
         <v>47</v>
       </c>
-      <c r="D11" t="n">
-        <v>42</v>
-      </c>
-      <c r="E11" t="n">
-        <v>48</v>
-      </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Weather &amp; Climate</t>
+          <t>Motion &amp; Time</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2915,31 +2903,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
+        <v>83</v>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="n">
         <v>80</v>
       </c>
-      <c r="E12" t="n">
-        <v>85</v>
-      </c>
-      <c r="F12" t="n">
-        <v>79</v>
-      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
+          <t>Weather &amp; Climate</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -2950,13 +2938,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C13" t="n">
+        <v>55</v>
+      </c>
+      <c r="D13" t="n">
         <v>57</v>
-      </c>
-      <c r="D13" t="n">
-        <v>59</v>
       </c>
       <c r="E13" t="n">
         <v>61</v>
@@ -2967,10 +2955,14 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Heat</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -2981,26 +2973,26 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
+          <t>Motion &amp; Time</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -3012,24 +3004,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Nutrition in Plants</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -3039,19 +3035,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
         <v>32</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -3070,28 +3066,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -3101,33 +3093,29 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>52</v>
+      </c>
+      <c r="C18" t="n">
+        <v>56</v>
+      </c>
+      <c r="D18" t="n">
+        <v>61</v>
+      </c>
+      <c r="E18" t="n">
+        <v>57</v>
+      </c>
+      <c r="F18" t="n">
         <v>63</v>
       </c>
-      <c r="C18" t="n">
-        <v>73</v>
-      </c>
-      <c r="D18" t="n">
-        <v>69</v>
-      </c>
-      <c r="E18" t="n">
-        <v>71</v>
-      </c>
-      <c r="F18" t="n">
-        <v>64</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Needs attention — performance has slipped recently.</t>
-        </is>
-      </c>
+          <t>Heat</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3136,26 +3124,26 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Nutrition in Plants</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3167,33 +3155,29 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>95</v>
+      </c>
+      <c r="C20" t="n">
+        <v>98</v>
+      </c>
+      <c r="D20" t="n">
         <v>97</v>
-      </c>
-      <c r="C20" t="n">
-        <v>88</v>
-      </c>
-      <c r="D20" t="n">
-        <v>91</v>
       </c>
       <c r="E20" t="n">
         <v>90</v>
       </c>
       <c r="F20" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Consistently excellent — ready for tougher challenges.</t>
-        </is>
-      </c>
+          <t>Motion &amp; Time</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3202,29 +3186,29 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E21" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3233,16 +3217,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C22" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D22" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
         <v>82</v>
@@ -3250,11 +3234,7 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Motion &amp; Time</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -3264,33 +3244,29 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C23" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D23" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E23" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Motion &amp; Time</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>On track, but should aim higher with focused practice.</t>
-        </is>
-      </c>
+          <t>Weather &amp; Climate</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3302,13 +3278,13 @@
         <v>54</v>
       </c>
       <c r="C24" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
         <v>54</v>
@@ -3316,7 +3292,11 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Motion &amp; Time</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -3326,29 +3306,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C25" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Below expectations — recommend extra classes after school.</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3357,24 +3333,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F26" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -3387,16 +3367,16 @@
         <v>20</v>
       </c>
       <c r="C27" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" t="n">
         <v>14</v>
       </c>
-      <c r="D27" t="n">
-        <v>23</v>
-      </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -3411,28 +3391,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C28" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F28" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Motion &amp; Time</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -3442,24 +3418,28 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>64</v>
+      </c>
+      <c r="C29" t="n">
+        <v>61</v>
+      </c>
+      <c r="D29" t="n">
+        <v>67</v>
+      </c>
+      <c r="E29" t="n">
+        <v>65</v>
+      </c>
+      <c r="F29" t="n">
         <v>68</v>
       </c>
-      <c r="C29" t="n">
-        <v>62</v>
-      </c>
-      <c r="D29" t="n">
-        <v>66</v>
-      </c>
-      <c r="E29" t="n">
-        <v>71</v>
-      </c>
-      <c r="F29" t="n">
-        <v>65</v>
-      </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Weather &amp; Climate</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -3469,26 +3449,26 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C30" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D30" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E30" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="F30" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3500,33 +3480,25 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>49</v>
+      </c>
+      <c r="C31" t="n">
+        <v>58</v>
+      </c>
+      <c r="D31" t="n">
+        <v>48</v>
+      </c>
+      <c r="E31" t="n">
+        <v>53</v>
+      </c>
+      <c r="F31" t="n">
         <v>52</v>
       </c>
-      <c r="C31" t="n">
-        <v>60</v>
-      </c>
-      <c r="D31" t="n">
-        <v>53</v>
-      </c>
-      <c r="E31" t="n">
-        <v>56</v>
-      </c>
-      <c r="F31" t="n">
-        <v>51</v>
-      </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Heat</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Encouraging progress, on the right track now.</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3607,26 +3579,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
         <v>43</v>
       </c>
       <c r="D2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2" t="n">
         <v>42</v>
       </c>
-      <c r="E2" t="n">
-        <v>41</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41</v>
-      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reading Comprehension</t>
+          <t>Letter Writing</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3638,19 +3610,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3660,11 +3632,7 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3673,28 +3641,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D4" t="n">
         <v>33</v>
       </c>
-      <c r="D4" t="n">
-        <v>30</v>
-      </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -3704,19 +3668,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3735,25 +3699,33 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Struggling with fundamentals, needs remedial sessions.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3762,33 +3734,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3797,24 +3761,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -3824,29 +3792,33 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
         <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Reading Comprehension</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3855,24 +3827,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -3882,28 +3858,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" t="n">
         <v>28</v>
       </c>
-      <c r="E11" t="n">
-        <v>27</v>
-      </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -3913,26 +3885,26 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" t="n">
+        <v>38</v>
+      </c>
+      <c r="D12" t="n">
+        <v>39</v>
+      </c>
+      <c r="E12" t="n">
         <v>41</v>
       </c>
-      <c r="D12" t="n">
-        <v>43</v>
-      </c>
-      <c r="E12" t="n">
-        <v>45</v>
-      </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Reading Comprehension</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -3944,26 +3916,26 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>28</v>
+      </c>
+      <c r="C13" t="n">
         <v>27</v>
-      </c>
-      <c r="C13" t="n">
-        <v>29</v>
       </c>
       <c r="D13" t="n">
         <v>26</v>
       </c>
       <c r="E13" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" t="n">
         <v>29</v>
       </c>
-      <c r="F13" t="n">
-        <v>31</v>
-      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -3975,19 +3947,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4002,28 +3974,24 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>25</v>
+      </c>
+      <c r="C15" t="n">
+        <v>22</v>
+      </c>
+      <c r="D15" t="n">
+        <v>21</v>
+      </c>
+      <c r="E15" t="n">
         <v>24</v>
       </c>
-      <c r="C15" t="n">
-        <v>21</v>
-      </c>
-      <c r="D15" t="n">
-        <v>20</v>
-      </c>
-      <c r="E15" t="n">
-        <v>22</v>
-      </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4036,23 +4004,23 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reading Comprehension</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -4064,19 +4032,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -4091,26 +4059,26 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
+          <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -4122,33 +4090,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>On track, but should aim higher with focused practice.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4157,7 +4117,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" t="n">
         <v>44</v>
@@ -4166,10 +4126,10 @@
         <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -4184,22 +4144,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D21" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4215,33 +4175,29 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
-        </is>
-      </c>
+          <t>Reading Comprehension</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4250,29 +4206,29 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
         <v>30</v>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4281,28 +4237,24 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>26</v>
+      </c>
+      <c r="C24" t="n">
+        <v>27</v>
+      </c>
+      <c r="D24" t="n">
+        <v>27</v>
+      </c>
+      <c r="E24" t="n">
+        <v>29</v>
+      </c>
+      <c r="F24" t="n">
         <v>30</v>
       </c>
-      <c r="C24" t="n">
-        <v>33</v>
-      </c>
-      <c r="D24" t="n">
-        <v>33</v>
-      </c>
-      <c r="E24" t="n">
-        <v>32</v>
-      </c>
-      <c r="F24" t="n">
-        <v>32</v>
-      </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Letter Writing</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -4312,26 +4264,26 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
         <v>19</v>
       </c>
-      <c r="C25" t="n">
-        <v>16</v>
-      </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
+          <t>Letter Writing</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -4343,24 +4295,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -4370,10 +4326,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
         <v>14</v>
@@ -4382,16 +4338,12 @@
         <v>14</v>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -4401,26 +4353,26 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4432,33 +4384,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C29" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D29" t="n">
         <v>31</v>
       </c>
       <c r="E29" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4467,16 +4411,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C30" t="n">
+        <v>48</v>
+      </c>
+      <c r="D30" t="n">
         <v>49</v>
       </c>
-      <c r="D30" t="n">
-        <v>50</v>
-      </c>
       <c r="E30" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F30" t="n">
         <v>45</v>
@@ -4494,29 +4438,33 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C31" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D31" t="n">
         <v>34</v>
       </c>
       <c r="E31" t="n">
+        <v>35</v>
+      </c>
+      <c r="F31" t="n">
         <v>32</v>
       </c>
-      <c r="F31" t="n">
-        <v>33</v>
-      </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Letter Writing</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Great turnaround this term, keep the momentum going!</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4597,16 +4545,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C2" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F2" t="n">
         <v>80</v>
@@ -4616,12 +4564,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -4632,19 +4580,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4670,25 +4618,21 @@
         <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Gadya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -4702,31 +4646,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
+        <v>41</v>
+      </c>
+      <c r="D5" t="n">
+        <v>43</v>
+      </c>
+      <c r="E5" t="n">
         <v>40</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>40</v>
       </c>
-      <c r="E5" t="n">
-        <v>45</v>
-      </c>
-      <c r="F5" t="n">
-        <v>37</v>
-      </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Below expectations — recommend extra classes after school.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -4737,20 +4681,20 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" t="n">
         <v>43</v>
       </c>
-      <c r="E6" t="n">
-        <v>35</v>
-      </c>
-      <c r="F6" t="n">
-        <v>45</v>
-      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
@@ -4761,7 +4705,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
+          <t>Below expectations — recommend extra classes after school.</t>
         </is>
       </c>
     </row>
@@ -4772,22 +4716,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4807,31 +4751,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Gadya Pathya 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Needs attention — performance has slipped recently.</t>
+          <t>Was doing well earlier, something seems to be affecting focus now.</t>
         </is>
       </c>
     </row>
@@ -4842,19 +4786,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4866,7 +4810,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -4877,31 +4821,27 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D10" t="n">
+        <v>98</v>
+      </c>
+      <c r="E10" t="n">
         <v>97</v>
       </c>
-      <c r="D10" t="n">
-        <v>97</v>
-      </c>
-      <c r="E10" t="n">
-        <v>90</v>
-      </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Gadya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Exceptional performance, keep up this standard.</t>
+          <t>Consistently excellent — ready for tougher challenges.</t>
         </is>
       </c>
     </row>
@@ -4912,24 +4852,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C11" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -4943,27 +4887,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" t="n">
+        <v>86</v>
+      </c>
+      <c r="F12" t="n">
         <v>85</v>
       </c>
-      <c r="E12" t="n">
-        <v>91</v>
-      </c>
-      <c r="F12" t="n">
-        <v>88</v>
-      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
+          <t>Strong performer, small gains possible with more practice.</t>
         </is>
       </c>
     </row>
@@ -4974,27 +4922,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -5005,19 +4953,19 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>67</v>
+      </c>
+      <c r="C14" t="n">
         <v>62</v>
       </c>
-      <c r="C14" t="n">
-        <v>68</v>
-      </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -5025,7 +4973,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -5036,24 +4984,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>Finding it difficult to keep pace, needs individual attention.</t>
@@ -5067,16 +5019,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C16" t="n">
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
         <v>34</v>
@@ -5086,12 +5038,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Gadya Pathya 1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Below expectations — recommend extra classes after school.</t>
+          <t>Struggling with fundamentals, needs remedial sessions.</t>
         </is>
       </c>
     </row>
@@ -5102,31 +5054,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Very low scores across the board, please involve parents.</t>
+          <t>Needs urgent academic support, at risk of failing.</t>
         </is>
       </c>
     </row>
@@ -5137,19 +5089,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -5168,31 +5120,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F19" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -5203,28 +5155,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C20" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D20" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F20" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Padya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Consistently excellent — ready for tougher challenges.</t>
@@ -5238,31 +5186,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C21" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F21" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Encouraging progress, on the right track now.</t>
+          <t>Visible improvement — the extra effort is showing results.</t>
         </is>
       </c>
     </row>
@@ -5276,21 +5224,25 @@
         <v>77</v>
       </c>
       <c r="C22" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D22" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E22" t="n">
+        <v>82</v>
+      </c>
+      <c r="F22" t="n">
         <v>85</v>
       </c>
-      <c r="F22" t="n">
-        <v>82</v>
-      </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -5304,24 +5256,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C23" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5335,19 +5291,19 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>59</v>
+      </c>
+      <c r="C24" t="n">
+        <v>64</v>
+      </c>
+      <c r="D24" t="n">
         <v>56</v>
       </c>
-      <c r="C24" t="n">
-        <v>61</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>55</v>
       </c>
-      <c r="E24" t="n">
-        <v>58</v>
-      </c>
       <c r="F24" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5366,31 +5322,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C25" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D25" t="n">
+        <v>40</v>
+      </c>
+      <c r="E25" t="n">
         <v>36</v>
       </c>
-      <c r="E25" t="n">
-        <v>40</v>
-      </c>
       <c r="F25" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Gadya Pathya 1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -5401,26 +5357,26 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C26" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D26" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Gadya Pathya 1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -5436,27 +5392,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Gadya Pathya 1</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Serious concern — immediate intervention needed.</t>
+          <t>Very low scores across the board, please involve parents.</t>
         </is>
       </c>
     </row>
@@ -5467,31 +5427,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E28" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Was doing well earlier, something seems to be affecting focus now.</t>
+          <t>Needs attention — performance has slipped recently.</t>
         </is>
       </c>
     </row>
@@ -5502,31 +5462,27 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>65</v>
+      </c>
+      <c r="C29" t="n">
+        <v>67</v>
+      </c>
+      <c r="D29" t="n">
+        <v>71</v>
+      </c>
+      <c r="E29" t="n">
         <v>69</v>
       </c>
-      <c r="C29" t="n">
-        <v>63</v>
-      </c>
-      <c r="D29" t="n">
-        <v>62</v>
-      </c>
-      <c r="E29" t="n">
-        <v>60</v>
-      </c>
       <c r="F29" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Gadya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -5537,27 +5493,31 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>89</v>
+      </c>
+      <c r="C30" t="n">
         <v>95</v>
       </c>
-      <c r="C30" t="n">
-        <v>86</v>
-      </c>
       <c r="D30" t="n">
+        <v>97</v>
+      </c>
+      <c r="E30" t="n">
         <v>91</v>
       </c>
-      <c r="E30" t="n">
-        <v>94</v>
-      </c>
       <c r="F30" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
+          <t>Consistently excellent — ready for tougher challenges.</t>
         </is>
       </c>
     </row>
@@ -5568,19 +5528,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C31" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D31" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E31" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F31" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -5592,7 +5552,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Encouraging progress, on the right track now.</t>
+          <t>Visible improvement — the extra effort is showing results.</t>
         </is>
       </c>
     </row>

--- a/samples/Sample_8_For_School_Management_Section_B_Class7.xlsx
+++ b/samples/Sample_8_For_School_Management_Section_B_Class7.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETUP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Test 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mid-Term" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Test 2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Exam" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7B-Unit Test 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7B-Mid-Term" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7B-Unit Test 2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7B-Final Exam" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -637,7 +637,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unit Test 1</t>
+          <t>Class7B-Unit Test 1</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mid-Term</t>
+          <t>Class7B-Mid-Term</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unit Test 2</t>
+          <t>Class7B-Unit Test 2</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Final Exam</t>
+          <t>Class7B-Final Exam</t>
         </is>
       </c>
     </row>
@@ -1632,8 +1632,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1664,7 +1662,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1695,7 +1692,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1721,8 +1717,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1753,7 +1747,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1784,7 +1777,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1815,7 +1807,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1846,7 +1837,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1877,7 +1867,6 @@
           <t>Perimeter &amp; Area</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1908,7 +1897,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1939,7 +1927,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1970,7 +1957,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2001,7 +1987,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2032,7 +2017,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2098,7 +2082,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2124,8 +2107,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2151,8 +2132,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2178,8 +2157,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2210,7 +2187,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2271,8 +2247,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2303,7 +2277,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2334,7 +2307,6 @@
           <t>Perimeter &amp; Area</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2360,8 +2332,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2387,7 +2357,6 @@
       <c r="G27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Serious concern — immediate intervention needed.</t>
@@ -2418,8 +2387,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2450,7 +2417,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2476,8 +2442,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2503,8 +2467,6 @@
       <c r="G31" t="n">
         <v>2</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2672,8 +2634,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2699,8 +2659,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2766,7 +2724,6 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2797,7 +2754,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2823,7 +2779,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -2894,7 +2849,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2995,7 +2949,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3026,7 +2979,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3057,7 +3009,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3083,8 +3034,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3115,7 +3064,6 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3146,7 +3094,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3177,7 +3124,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3208,7 +3154,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3234,8 +3179,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3266,7 +3209,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3297,7 +3239,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3323,8 +3264,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3355,7 +3294,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3381,8 +3319,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3408,8 +3344,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3440,7 +3374,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3471,7 +3404,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3497,8 +3429,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3601,7 +3531,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3632,7 +3561,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3658,8 +3586,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3690,7 +3616,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3751,8 +3676,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3783,7 +3706,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3849,7 +3771,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3875,8 +3796,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3907,7 +3826,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3938,7 +3856,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3964,8 +3881,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3991,8 +3906,6 @@
       <c r="G15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4023,7 +3936,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4049,8 +3961,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4081,7 +3991,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4107,8 +4016,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4134,8 +4041,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4166,7 +4071,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4197,7 +4101,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4223,7 +4126,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -4254,8 +4156,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4286,7 +4186,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4317,7 +4216,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4343,8 +4241,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4375,7 +4271,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4401,8 +4296,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4428,8 +4321,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4632,7 +4523,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -4838,7 +4728,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Consistently excellent — ready for tougher challenges.</t>
@@ -4939,7 +4828,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -4970,7 +4858,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -5106,7 +4993,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Needs attention — performance has slipped recently.</t>
@@ -5172,7 +5058,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Consistently excellent — ready for tougher challenges.</t>
@@ -5308,7 +5193,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -5479,7 +5363,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
